--- a/artfynd/A 18485-2025 artfynd.xlsx
+++ b/artfynd/A 18485-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124188078</v>
+        <v>124217147</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,32 +708,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Norrlången, Norrlången, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595039</v>
+        <v>595216</v>
       </c>
       <c r="R2" t="n">
-        <v>6567586</v>
+        <v>6567597</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124217147</v>
+        <v>124188078</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>57883</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,20 +804,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -837,20 +825,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Norrlången, Norrlången, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595216</v>
+        <v>595039</v>
       </c>
       <c r="R3" t="n">
-        <v>6567597</v>
+        <v>6567586</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 18485-2025 artfynd.xlsx
+++ b/artfynd/A 18485-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -919,6 +919,123 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124691077</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91032</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vretlund, Vretlund, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>595902</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6567429</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Hällmarksbarrskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18485-2025 artfynd.xlsx
+++ b/artfynd/A 18485-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124217147</v>
+        <v>124188078</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>57883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,20 +708,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Norrlången, Norrlången, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595216</v>
+        <v>595039</v>
       </c>
       <c r="R2" t="n">
-        <v>6567597</v>
+        <v>6567586</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124188078</v>
+        <v>124217147</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,20 +816,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -825,32 +837,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Norrlången, Norrlången, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595039</v>
+        <v>595216</v>
       </c>
       <c r="R3" t="n">
-        <v>6567586</v>
+        <v>6567597</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 18485-2025 artfynd.xlsx
+++ b/artfynd/A 18485-2025 artfynd.xlsx
@@ -924,7 +924,7 @@
         <v>124691077</v>
       </c>
       <c r="B4" t="n">
-        <v>91032</v>
+        <v>91186</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
